--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3272" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21AB5F01-921C-42DF-8042-D5B31F9372B9}"/>
+  <xr:revisionPtr revIDLastSave="3394" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701281F2-DD33-4AF7-B2B5-DAD8AB44E905}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="140">
   <si>
     <t>Boneco</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>Tanaka</t>
+  </si>
+  <si>
+    <t>Davi</t>
   </si>
 </sst>
 </file>
@@ -782,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O206"/>
+  <dimension ref="A1:O229"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -8021,6 +8024,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>115</v>
+      </c>
+      <c r="C207">
+        <v>3</v>
+      </c>
+      <c r="D207">
+        <v>2</v>
+      </c>
+      <c r="E207">
+        <v>2</v>
+      </c>
+      <c r="F207">
+        <v>3</v>
+      </c>
+      <c r="G207">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>41</v>
+      </c>
+      <c r="C208">
+        <v>3</v>
+      </c>
+      <c r="D208">
+        <v>2</v>
+      </c>
+      <c r="E208">
+        <v>2</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208">
+        <v>1</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>28</v>
+      </c>
+      <c r="C209">
+        <v>3</v>
+      </c>
+      <c r="D209">
+        <v>2</v>
+      </c>
+      <c r="E209">
+        <v>2</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>1</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>0</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>4</v>
+      </c>
+      <c r="C210">
+        <v>3</v>
+      </c>
+      <c r="D210">
+        <v>2</v>
+      </c>
+      <c r="E210">
+        <v>2</v>
+      </c>
+      <c r="F210">
+        <v>3</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>57</v>
+      </c>
+      <c r="C211">
+        <v>3</v>
+      </c>
+      <c r="D211">
+        <v>2</v>
+      </c>
+      <c r="E211">
+        <v>2</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>2</v>
+      </c>
+      <c r="C212">
+        <v>5</v>
+      </c>
+      <c r="D212">
+        <v>2</v>
+      </c>
+      <c r="E212">
+        <v>3</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>1</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>139</v>
+      </c>
+      <c r="C213">
+        <v>5</v>
+      </c>
+      <c r="D213">
+        <v>2</v>
+      </c>
+      <c r="E213">
+        <v>3</v>
+      </c>
+      <c r="F213">
+        <v>2</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+      <c r="H213">
+        <v>1</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>21</v>
+      </c>
+      <c r="C214">
+        <v>5</v>
+      </c>
+      <c r="D214">
+        <v>2</v>
+      </c>
+      <c r="E214">
+        <v>3</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>5</v>
+      </c>
+      <c r="C215">
+        <v>5</v>
+      </c>
+      <c r="D215">
+        <v>2</v>
+      </c>
+      <c r="E215">
+        <v>3</v>
+      </c>
+      <c r="F215">
+        <v>2</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>1</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>33</v>
+      </c>
+      <c r="C216">
+        <v>5</v>
+      </c>
+      <c r="D216">
+        <v>2</v>
+      </c>
+      <c r="E216">
+        <v>3</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+      <c r="H216">
+        <v>1</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>0</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>84</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+      <c r="D217">
+        <v>2</v>
+      </c>
+      <c r="E217">
+        <v>4</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>59</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+      <c r="D218">
+        <v>2</v>
+      </c>
+      <c r="E218">
+        <v>4</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>1</v>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+      <c r="D219">
+        <v>2</v>
+      </c>
+      <c r="E219">
+        <v>4</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>30</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+      <c r="D220">
+        <v>2</v>
+      </c>
+      <c r="E220">
+        <v>4</v>
+      </c>
+      <c r="F220">
+        <v>1</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>6</v>
+      </c>
+      <c r="C221">
+        <v>2</v>
+      </c>
+      <c r="D221">
+        <v>2</v>
+      </c>
+      <c r="E221">
+        <v>4</v>
+      </c>
+      <c r="F221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221">
+        <v>0</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>130</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222">
+        <v>2</v>
+      </c>
+      <c r="E222">
+        <v>3</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>32</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223">
+        <v>2</v>
+      </c>
+      <c r="E223">
+        <v>3</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223">
+        <v>1</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>20</v>
+      </c>
+      <c r="C224">
+        <v>2</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+      <c r="E224">
+        <v>3</v>
+      </c>
+      <c r="F224">
+        <v>0</v>
+      </c>
+      <c r="G224">
+        <v>1</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>27</v>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+      <c r="D225">
+        <v>2</v>
+      </c>
+      <c r="E225">
+        <v>3</v>
+      </c>
+      <c r="F225">
+        <v>2</v>
+      </c>
+      <c r="G225">
+        <v>1</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226">
+        <v>2</v>
+      </c>
+      <c r="D226">
+        <v>2</v>
+      </c>
+      <c r="E226">
+        <v>3</v>
+      </c>
+      <c r="F226">
+        <v>2</v>
+      </c>
+      <c r="G226">
+        <v>1</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>107</v>
+      </c>
+      <c r="C227">
+        <v>5</v>
+      </c>
+      <c r="D227">
+        <v>4</v>
+      </c>
+      <c r="E227">
+        <v>4</v>
+      </c>
+      <c r="F227">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>1</v>
+      </c>
+      <c r="H227">
+        <v>1</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>10</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>111</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>3</v>
+      </c>
+      <c r="F228">
+        <v>0</v>
+      </c>
+      <c r="G228">
+        <v>1</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>4</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>45</v>
+      </c>
+      <c r="C229">
+        <v>5</v>
+      </c>
+      <c r="D229">
+        <v>4</v>
+      </c>
+      <c r="E229">
+        <v>4</v>
+      </c>
+      <c r="F229">
+        <v>0</v>
+      </c>
+      <c r="G229">
+        <v>1</v>
+      </c>
+      <c r="H229">
+        <v>1</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>10</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3394" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701281F2-DD33-4AF7-B2B5-DAD8AB44E905}"/>
+  <xr:revisionPtr revIDLastSave="3509" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BECF13D-858D-4036-9633-FEE2F3FD44BB}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="140">
   <si>
     <t>Boneco</t>
   </si>
@@ -785,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O229"/>
+  <dimension ref="A1:O251"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -8829,6 +8829,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>2</v>
+      </c>
+      <c r="C230">
+        <v>4</v>
+      </c>
+      <c r="D230">
+        <v>2</v>
+      </c>
+      <c r="E230">
+        <v>3</v>
+      </c>
+      <c r="F230">
+        <v>4</v>
+      </c>
+      <c r="G230">
+        <v>1</v>
+      </c>
+      <c r="H230">
+        <v>1</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231">
+        <v>4</v>
+      </c>
+      <c r="D231">
+        <v>2</v>
+      </c>
+      <c r="E231">
+        <v>3</v>
+      </c>
+      <c r="F231">
+        <v>2</v>
+      </c>
+      <c r="G231">
+        <v>1</v>
+      </c>
+      <c r="H231">
+        <v>1</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>28</v>
+      </c>
+      <c r="C232">
+        <v>4</v>
+      </c>
+      <c r="D232">
+        <v>2</v>
+      </c>
+      <c r="E232">
+        <v>3</v>
+      </c>
+      <c r="F232">
+        <v>1</v>
+      </c>
+      <c r="G232">
+        <v>1</v>
+      </c>
+      <c r="H232">
+        <v>1</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>23</v>
+      </c>
+      <c r="C233">
+        <v>4</v>
+      </c>
+      <c r="D233">
+        <v>2</v>
+      </c>
+      <c r="E233">
+        <v>3</v>
+      </c>
+      <c r="F233">
+        <v>0</v>
+      </c>
+      <c r="G233">
+        <v>1</v>
+      </c>
+      <c r="H233">
+        <v>1</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>41</v>
+      </c>
+      <c r="C234">
+        <v>4</v>
+      </c>
+      <c r="D234">
+        <v>2</v>
+      </c>
+      <c r="E234">
+        <v>3</v>
+      </c>
+      <c r="F234">
+        <v>0</v>
+      </c>
+      <c r="G234">
+        <v>1</v>
+      </c>
+      <c r="H234">
+        <v>1</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>26</v>
+      </c>
+      <c r="C235">
+        <v>2</v>
+      </c>
+      <c r="D235">
+        <v>4</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
+      <c r="F235">
+        <v>0</v>
+      </c>
+      <c r="G235">
+        <v>1</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>30</v>
+      </c>
+      <c r="C236">
+        <v>2</v>
+      </c>
+      <c r="D236">
+        <v>4</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236">
+        <v>1</v>
+      </c>
+      <c r="G236">
+        <v>1</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>4</v>
+      </c>
+      <c r="C237">
+        <v>2</v>
+      </c>
+      <c r="D237">
+        <v>4</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+      <c r="F237">
+        <v>3</v>
+      </c>
+      <c r="G237">
+        <v>1</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>59</v>
+      </c>
+      <c r="C238">
+        <v>2</v>
+      </c>
+      <c r="D238">
+        <v>4</v>
+      </c>
+      <c r="E238">
+        <v>1</v>
+      </c>
+      <c r="F238">
+        <v>0</v>
+      </c>
+      <c r="G238">
+        <v>1</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>6</v>
+      </c>
+      <c r="C239">
+        <v>2</v>
+      </c>
+      <c r="D239">
+        <v>4</v>
+      </c>
+      <c r="E239">
+        <v>1</v>
+      </c>
+      <c r="F239">
+        <v>1</v>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>33</v>
+      </c>
+      <c r="C240">
+        <v>2</v>
+      </c>
+      <c r="D240">
+        <v>2</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
+      <c r="F240">
+        <v>2</v>
+      </c>
+      <c r="G240">
+        <v>1</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>90</v>
+      </c>
+      <c r="C241">
+        <v>2</v>
+      </c>
+      <c r="D241">
+        <v>2</v>
+      </c>
+      <c r="E241">
+        <v>3</v>
+      </c>
+      <c r="F241">
+        <v>0</v>
+      </c>
+      <c r="G241">
+        <v>1</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>57</v>
+      </c>
+      <c r="C242">
+        <v>2</v>
+      </c>
+      <c r="D242">
+        <v>2</v>
+      </c>
+      <c r="E242">
+        <v>3</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242">
+        <v>1</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>1</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243">
+        <v>2</v>
+      </c>
+      <c r="E243">
+        <v>3</v>
+      </c>
+      <c r="F243">
+        <v>0</v>
+      </c>
+      <c r="G243">
+        <v>1</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>21</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+      <c r="D244">
+        <v>2</v>
+      </c>
+      <c r="E244">
+        <v>3</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244">
+        <v>1</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>0</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+      <c r="D245">
+        <v>2</v>
+      </c>
+      <c r="E245">
+        <v>3</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245">
+        <v>1</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>1</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>27</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+      <c r="D246">
+        <v>2</v>
+      </c>
+      <c r="E246">
+        <v>3</v>
+      </c>
+      <c r="F246">
+        <v>2</v>
+      </c>
+      <c r="G246">
+        <v>1</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247">
+        <v>2</v>
+      </c>
+      <c r="D247">
+        <v>2</v>
+      </c>
+      <c r="E247">
+        <v>3</v>
+      </c>
+      <c r="F247">
+        <v>0</v>
+      </c>
+      <c r="G247">
+        <v>1</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>0</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248">
+        <v>2</v>
+      </c>
+      <c r="D248">
+        <v>2</v>
+      </c>
+      <c r="E248">
+        <v>3</v>
+      </c>
+      <c r="F248">
+        <v>0</v>
+      </c>
+      <c r="G248">
+        <v>1</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>109</v>
+      </c>
+      <c r="C249">
+        <v>2</v>
+      </c>
+      <c r="D249">
+        <v>2</v>
+      </c>
+      <c r="E249">
+        <v>3</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+      <c r="G249">
+        <v>1</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>0</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>17</v>
+      </c>
+      <c r="C250">
+        <v>4</v>
+      </c>
+      <c r="D250">
+        <v>5</v>
+      </c>
+      <c r="E250">
+        <v>5</v>
+      </c>
+      <c r="F250">
+        <v>0</v>
+      </c>
+      <c r="G250">
+        <v>1</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>1</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>10</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>80</v>
+      </c>
+      <c r="C251">
+        <v>5</v>
+      </c>
+      <c r="D251">
+        <v>5</v>
+      </c>
+      <c r="E251">
+        <v>4</v>
+      </c>
+      <c r="F251">
+        <v>1</v>
+      </c>
+      <c r="G251">
+        <v>1</v>
+      </c>
+      <c r="H251">
+        <v>1</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>11</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3509" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BECF13D-858D-4036-9633-FEE2F3FD44BB}"/>
+  <xr:revisionPtr revIDLastSave="3640" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10709F97-2E85-42EC-ABA4-272E167F3F18}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
   <si>
     <t>Boneco</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t>Davi</t>
+  </si>
+  <si>
+    <t>Lukinha</t>
   </si>
 </sst>
 </file>
@@ -785,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O251"/>
+  <dimension ref="A1:O274"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -9599,6 +9602,811 @@
         <v>0</v>
       </c>
     </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>26</v>
+      </c>
+      <c r="C252">
+        <v>3</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>6</v>
+      </c>
+      <c r="F252">
+        <v>0</v>
+      </c>
+      <c r="G252">
+        <v>1</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>1</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>57</v>
+      </c>
+      <c r="C253">
+        <v>3</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>6</v>
+      </c>
+      <c r="F253">
+        <v>2</v>
+      </c>
+      <c r="G253">
+        <v>1</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>1</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>32</v>
+      </c>
+      <c r="C254">
+        <v>3</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>6</v>
+      </c>
+      <c r="F254">
+        <v>0</v>
+      </c>
+      <c r="G254">
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>1</v>
+      </c>
+      <c r="C255">
+        <v>3</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>6</v>
+      </c>
+      <c r="F255">
+        <v>4</v>
+      </c>
+      <c r="G255">
+        <v>1</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>0</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256">
+        <v>3</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>6</v>
+      </c>
+      <c r="F256">
+        <v>1</v>
+      </c>
+      <c r="G256">
+        <v>1</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>0</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>34</v>
+      </c>
+      <c r="C257">
+        <v>6</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257">
+        <v>3</v>
+      </c>
+      <c r="F257">
+        <v>2</v>
+      </c>
+      <c r="G257">
+        <v>1</v>
+      </c>
+      <c r="H257">
+        <v>1</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>33</v>
+      </c>
+      <c r="C258">
+        <v>6</v>
+      </c>
+      <c r="D258">
+        <v>1</v>
+      </c>
+      <c r="E258">
+        <v>3</v>
+      </c>
+      <c r="F258">
+        <v>6</v>
+      </c>
+      <c r="G258">
+        <v>1</v>
+      </c>
+      <c r="H258">
+        <v>1</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>0</v>
+      </c>
+      <c r="L258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>90</v>
+      </c>
+      <c r="C259">
+        <v>6</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+      <c r="E259">
+        <v>3</v>
+      </c>
+      <c r="F259">
+        <v>1</v>
+      </c>
+      <c r="G259">
+        <v>1</v>
+      </c>
+      <c r="H259">
+        <v>1</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259">
+        <v>0</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260">
+        <v>6</v>
+      </c>
+      <c r="D260">
+        <v>1</v>
+      </c>
+      <c r="E260">
+        <v>3</v>
+      </c>
+      <c r="F260">
+        <v>3</v>
+      </c>
+      <c r="G260">
+        <v>1</v>
+      </c>
+      <c r="H260">
+        <v>1</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>140</v>
+      </c>
+      <c r="C261">
+        <v>6</v>
+      </c>
+      <c r="D261">
+        <v>1</v>
+      </c>
+      <c r="E261">
+        <v>3</v>
+      </c>
+      <c r="F261">
+        <v>2</v>
+      </c>
+      <c r="G261">
+        <v>1</v>
+      </c>
+      <c r="H261">
+        <v>1</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>20</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262">
+        <v>2</v>
+      </c>
+      <c r="E262">
+        <v>3</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+      <c r="G262">
+        <v>1</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>2</v>
+      </c>
+      <c r="C263">
+        <v>3</v>
+      </c>
+      <c r="D263">
+        <v>2</v>
+      </c>
+      <c r="E263">
+        <v>3</v>
+      </c>
+      <c r="F263">
+        <v>4</v>
+      </c>
+      <c r="G263">
+        <v>1</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>41</v>
+      </c>
+      <c r="C264">
+        <v>3</v>
+      </c>
+      <c r="D264">
+        <v>2</v>
+      </c>
+      <c r="E264">
+        <v>3</v>
+      </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
+      <c r="G264">
+        <v>1</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>30</v>
+      </c>
+      <c r="C265">
+        <v>3</v>
+      </c>
+      <c r="D265">
+        <v>2</v>
+      </c>
+      <c r="E265">
+        <v>3</v>
+      </c>
+      <c r="F265">
+        <v>2</v>
+      </c>
+      <c r="G265">
+        <v>1</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>0</v>
+      </c>
+      <c r="L265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>5</v>
+      </c>
+      <c r="C266">
+        <v>3</v>
+      </c>
+      <c r="D266">
+        <v>2</v>
+      </c>
+      <c r="E266">
+        <v>3</v>
+      </c>
+      <c r="F266">
+        <v>2</v>
+      </c>
+      <c r="G266">
+        <v>1</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>0</v>
+      </c>
+      <c r="L266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>59</v>
+      </c>
+      <c r="C267">
+        <v>4</v>
+      </c>
+      <c r="D267">
+        <v>1</v>
+      </c>
+      <c r="E267">
+        <v>4</v>
+      </c>
+      <c r="F267">
+        <v>2</v>
+      </c>
+      <c r="G267">
+        <v>1</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>0</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>28</v>
+      </c>
+      <c r="C268">
+        <v>4</v>
+      </c>
+      <c r="D268">
+        <v>1</v>
+      </c>
+      <c r="E268">
+        <v>4</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+      <c r="G268">
+        <v>1</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>0</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269">
+        <v>4</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+      <c r="E269">
+        <v>4</v>
+      </c>
+      <c r="F269">
+        <v>5</v>
+      </c>
+      <c r="G269">
+        <v>1</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>0</v>
+      </c>
+      <c r="L269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>27</v>
+      </c>
+      <c r="C270">
+        <v>4</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+      <c r="E270">
+        <v>4</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+      <c r="G270">
+        <v>1</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>0</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>130</v>
+      </c>
+      <c r="C271">
+        <v>4</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+      <c r="E271">
+        <v>4</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271">
+        <v>1</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>0</v>
+      </c>
+      <c r="L271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>17</v>
+      </c>
+      <c r="C272">
+        <v>7</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>6</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272">
+        <v>1</v>
+      </c>
+      <c r="H272">
+        <v>1</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>12</v>
+      </c>
+      <c r="L272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>45</v>
+      </c>
+      <c r="C273">
+        <v>2</v>
+      </c>
+      <c r="D273">
+        <v>2</v>
+      </c>
+      <c r="E273">
+        <v>4</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273">
+        <v>1</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273">
+        <v>1</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>10</v>
+      </c>
+      <c r="L273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>80</v>
+      </c>
+      <c r="C274">
+        <v>6</v>
+      </c>
+      <c r="D274">
+        <v>2</v>
+      </c>
+      <c r="E274">
+        <v>5</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
+        <v>1</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>15</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3640" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10709F97-2E85-42EC-ABA4-272E167F3F18}"/>
+  <xr:revisionPtr revIDLastSave="3757" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37332E36-D8EB-4499-903C-54BD07E42544}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jogadores" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
   <si>
     <t>Boneco</t>
   </si>
@@ -788,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O274"/>
+  <dimension ref="A1:O296"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C149">
         <v>4</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8344,7 +8344,7 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C216">
         <v>5</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C240">
         <v>2</v>
@@ -9814,7 +9814,7 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C258">
         <v>6</v>
@@ -10404,6 +10404,776 @@
         <v>15</v>
       </c>
       <c r="L274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>30</v>
+      </c>
+      <c r="C275">
+        <v>2</v>
+      </c>
+      <c r="D275">
+        <v>3</v>
+      </c>
+      <c r="E275">
+        <v>2</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275">
+        <v>1</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>0</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>0</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>36</v>
+      </c>
+      <c r="C276">
+        <v>2</v>
+      </c>
+      <c r="D276">
+        <v>3</v>
+      </c>
+      <c r="E276">
+        <v>2</v>
+      </c>
+      <c r="F276">
+        <v>5</v>
+      </c>
+      <c r="G276">
+        <v>1</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>6</v>
+      </c>
+      <c r="C277">
+        <v>2</v>
+      </c>
+      <c r="D277">
+        <v>3</v>
+      </c>
+      <c r="E277">
+        <v>2</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+      <c r="G277">
+        <v>1</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>0</v>
+      </c>
+      <c r="L277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>41</v>
+      </c>
+      <c r="C278">
+        <v>2</v>
+      </c>
+      <c r="D278">
+        <v>3</v>
+      </c>
+      <c r="E278">
+        <v>2</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+      <c r="G278">
+        <v>1</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>0</v>
+      </c>
+      <c r="L278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>115</v>
+      </c>
+      <c r="C279">
+        <v>2</v>
+      </c>
+      <c r="D279">
+        <v>3</v>
+      </c>
+      <c r="E279">
+        <v>2</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+      <c r="G279">
+        <v>1</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+      <c r="L279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>34</v>
+      </c>
+      <c r="C280">
+        <v>5</v>
+      </c>
+      <c r="D280">
+        <v>3</v>
+      </c>
+      <c r="E280">
+        <v>2</v>
+      </c>
+      <c r="F280">
+        <v>2</v>
+      </c>
+      <c r="G280">
+        <v>1</v>
+      </c>
+      <c r="H280">
+        <v>1</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>59</v>
+      </c>
+      <c r="C281">
+        <v>5</v>
+      </c>
+      <c r="D281">
+        <v>3</v>
+      </c>
+      <c r="E281">
+        <v>2</v>
+      </c>
+      <c r="F281">
+        <v>2</v>
+      </c>
+      <c r="G281">
+        <v>1</v>
+      </c>
+      <c r="H281">
+        <v>1</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>0</v>
+      </c>
+      <c r="L281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>5</v>
+      </c>
+      <c r="C282">
+        <v>5</v>
+      </c>
+      <c r="D282">
+        <v>3</v>
+      </c>
+      <c r="E282">
+        <v>2</v>
+      </c>
+      <c r="F282">
+        <v>3</v>
+      </c>
+      <c r="G282">
+        <v>1</v>
+      </c>
+      <c r="H282">
+        <v>1</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>0</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>1</v>
+      </c>
+      <c r="C283">
+        <v>5</v>
+      </c>
+      <c r="D283">
+        <v>3</v>
+      </c>
+      <c r="E283">
+        <v>2</v>
+      </c>
+      <c r="F283">
+        <v>4</v>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>1</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>32</v>
+      </c>
+      <c r="C284">
+        <v>5</v>
+      </c>
+      <c r="D284">
+        <v>3</v>
+      </c>
+      <c r="E284">
+        <v>2</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+      <c r="G284">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>1</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>28</v>
+      </c>
+      <c r="C285">
+        <v>2</v>
+      </c>
+      <c r="D285">
+        <v>3</v>
+      </c>
+      <c r="E285">
+        <v>2</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+      <c r="G285">
+        <v>1</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>0</v>
+      </c>
+      <c r="L285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>27</v>
+      </c>
+      <c r="C286">
+        <v>2</v>
+      </c>
+      <c r="D286">
+        <v>3</v>
+      </c>
+      <c r="E286">
+        <v>2</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+      <c r="G286">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>2</v>
+      </c>
+      <c r="C287">
+        <v>2</v>
+      </c>
+      <c r="D287">
+        <v>3</v>
+      </c>
+      <c r="E287">
+        <v>2</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+      <c r="G287">
+        <v>1</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288">
+        <v>2</v>
+      </c>
+      <c r="D288">
+        <v>3</v>
+      </c>
+      <c r="E288">
+        <v>2</v>
+      </c>
+      <c r="F288">
+        <v>3</v>
+      </c>
+      <c r="G288">
+        <v>1</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>0</v>
+      </c>
+      <c r="L288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>20</v>
+      </c>
+      <c r="C289">
+        <v>2</v>
+      </c>
+      <c r="D289">
+        <v>3</v>
+      </c>
+      <c r="E289">
+        <v>2</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>1</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>0</v>
+      </c>
+      <c r="L289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>3</v>
+      </c>
+      <c r="E290">
+        <v>3</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+      <c r="G290">
+        <v>1</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>0</v>
+      </c>
+      <c r="L290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>57</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>3</v>
+      </c>
+      <c r="E291">
+        <v>3</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+      <c r="G291">
+        <v>1</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>0</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>130</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292">
+        <v>1</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>4</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>3</v>
+      </c>
+      <c r="E293">
+        <v>3</v>
+      </c>
+      <c r="F293">
+        <v>1</v>
+      </c>
+      <c r="G293">
+        <v>1</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>0</v>
+      </c>
+      <c r="L293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>26</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>3</v>
+      </c>
+      <c r="E294">
+        <v>3</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294">
+        <v>1</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>0</v>
+      </c>
+      <c r="L294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>17</v>
+      </c>
+      <c r="C295">
+        <v>2</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295">
+        <v>5</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>1</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>17</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>107</v>
+      </c>
+      <c r="C296">
+        <v>5</v>
+      </c>
+      <c r="D296">
+        <v>6</v>
+      </c>
+      <c r="E296">
+        <v>2</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>1</v>
+      </c>
+      <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="I296">
+        <v>0</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>8</v>
+      </c>
+      <c r="L296">
         <v>0</v>
       </c>
     </row>

--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3757" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37332E36-D8EB-4499-903C-54BD07E42544}"/>
+  <xr:revisionPtr revIDLastSave="3855" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA5B639C-6074-40C0-AE1C-9D9B37AB8E03}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="142">
   <si>
     <t>Boneco</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>Lukinha</t>
+  </si>
+  <si>
+    <t>Para</t>
   </si>
 </sst>
 </file>
@@ -788,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O296"/>
+  <dimension ref="A1:O320"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -11177,6 +11180,846 @@
         <v>0</v>
       </c>
     </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>109</v>
+      </c>
+      <c r="C297">
+        <v>3</v>
+      </c>
+      <c r="D297">
+        <v>3</v>
+      </c>
+      <c r="E297">
+        <v>1</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+      <c r="G297">
+        <v>1</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297">
+        <v>0</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>29</v>
+      </c>
+      <c r="C298">
+        <v>3</v>
+      </c>
+      <c r="D298">
+        <v>3</v>
+      </c>
+      <c r="E298">
+        <v>1</v>
+      </c>
+      <c r="F298">
+        <v>1</v>
+      </c>
+      <c r="G298">
+        <v>1</v>
+      </c>
+      <c r="H298">
+        <v>1</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>0</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>20</v>
+      </c>
+      <c r="C299">
+        <v>3</v>
+      </c>
+      <c r="D299">
+        <v>3</v>
+      </c>
+      <c r="E299">
+        <v>1</v>
+      </c>
+      <c r="F299">
+        <v>1</v>
+      </c>
+      <c r="G299">
+        <v>1</v>
+      </c>
+      <c r="H299">
+        <v>1</v>
+      </c>
+      <c r="I299">
+        <v>0</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>0</v>
+      </c>
+      <c r="L299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>5</v>
+      </c>
+      <c r="C300">
+        <v>3</v>
+      </c>
+      <c r="D300">
+        <v>3</v>
+      </c>
+      <c r="E300">
+        <v>1</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+      <c r="G300">
+        <v>1</v>
+      </c>
+      <c r="H300">
+        <v>1</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>4</v>
+      </c>
+      <c r="C301">
+        <v>3</v>
+      </c>
+      <c r="D301">
+        <v>3</v>
+      </c>
+      <c r="E301">
+        <v>1</v>
+      </c>
+      <c r="F301">
+        <v>1</v>
+      </c>
+      <c r="G301">
+        <v>1</v>
+      </c>
+      <c r="H301">
+        <v>1</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>2</v>
+      </c>
+      <c r="C302">
+        <v>2</v>
+      </c>
+      <c r="D302">
+        <v>3</v>
+      </c>
+      <c r="E302">
+        <v>1</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302">
+        <v>1</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>50</v>
+      </c>
+      <c r="C303">
+        <v>2</v>
+      </c>
+      <c r="D303">
+        <v>3</v>
+      </c>
+      <c r="E303">
+        <v>1</v>
+      </c>
+      <c r="F303">
+        <v>1</v>
+      </c>
+      <c r="G303">
+        <v>1</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>27</v>
+      </c>
+      <c r="C304">
+        <v>2</v>
+      </c>
+      <c r="D304">
+        <v>3</v>
+      </c>
+      <c r="E304">
+        <v>1</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>1</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305">
+        <v>2</v>
+      </c>
+      <c r="D305">
+        <v>3</v>
+      </c>
+      <c r="E305">
+        <v>1</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>1</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>0</v>
+      </c>
+      <c r="L305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>130</v>
+      </c>
+      <c r="C306">
+        <v>2</v>
+      </c>
+      <c r="D306">
+        <v>3</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
+      <c r="F306">
+        <v>1</v>
+      </c>
+      <c r="G306">
+        <v>1</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>6</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>4</v>
+      </c>
+      <c r="F307">
+        <v>1</v>
+      </c>
+      <c r="G307">
+        <v>1</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>1</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>36</v>
+      </c>
+      <c r="C308">
+        <v>2</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>4</v>
+      </c>
+      <c r="F308">
+        <v>1</v>
+      </c>
+      <c r="G308">
+        <v>1</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>1</v>
+      </c>
+      <c r="C309">
+        <v>2</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>4</v>
+      </c>
+      <c r="F309">
+        <v>1</v>
+      </c>
+      <c r="G309">
+        <v>1</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>1</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>26</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>4</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>1</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>137</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>4</v>
+      </c>
+      <c r="F311">
+        <v>1</v>
+      </c>
+      <c r="G311">
+        <v>1</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311">
+        <v>0</v>
+      </c>
+      <c r="K311">
+        <v>0</v>
+      </c>
+      <c r="L311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>115</v>
+      </c>
+      <c r="C312">
+        <v>3</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>4</v>
+      </c>
+      <c r="F312">
+        <v>2</v>
+      </c>
+      <c r="G312">
+        <v>1</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312">
+        <v>0</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>0</v>
+      </c>
+      <c r="L312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>82</v>
+      </c>
+      <c r="C313">
+        <v>3</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>4</v>
+      </c>
+      <c r="F313">
+        <v>3</v>
+      </c>
+      <c r="G313">
+        <v>1</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>25</v>
+      </c>
+      <c r="C314">
+        <v>3</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>4</v>
+      </c>
+      <c r="F314">
+        <v>0</v>
+      </c>
+      <c r="G314">
+        <v>1</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>30</v>
+      </c>
+      <c r="C315">
+        <v>3</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>4</v>
+      </c>
+      <c r="F315">
+        <v>1</v>
+      </c>
+      <c r="G315">
+        <v>1</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>0</v>
+      </c>
+      <c r="L315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>32</v>
+      </c>
+      <c r="C316">
+        <v>3</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>4</v>
+      </c>
+      <c r="F316">
+        <v>0</v>
+      </c>
+      <c r="G316">
+        <v>1</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>0</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>0</v>
+      </c>
+      <c r="L316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>107</v>
+      </c>
+      <c r="C317">
+        <v>3</v>
+      </c>
+      <c r="D317">
+        <v>3</v>
+      </c>
+      <c r="E317">
+        <v>1</v>
+      </c>
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317">
+        <v>1</v>
+      </c>
+      <c r="H317">
+        <v>1</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>1</v>
+      </c>
+      <c r="L317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>17</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+      <c r="D318">
+        <v>3</v>
+      </c>
+      <c r="E318">
+        <v>1</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>1</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+      <c r="I318">
+        <v>0</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>2</v>
+      </c>
+      <c r="L318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>45</v>
+      </c>
+      <c r="C319">
+        <v>2</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>4</v>
+      </c>
+      <c r="F319">
+        <v>1</v>
+      </c>
+      <c r="G319">
+        <v>1</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>7</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>141</v>
+      </c>
+      <c r="C320">
+        <v>3</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>4</v>
+      </c>
+      <c r="F320">
+        <v>0</v>
+      </c>
+      <c r="G320">
+        <v>1</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>7</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelada_sabado_2026_02.xlsx
+++ b/pelada_sabado_2026_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ritzferramentasltda-my.sharepoint.com/personal/fernando_almeida_ritzbrasil_com/Documents/Desktop/Nova pasta (2)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3855" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA5B639C-6074-40C0-AE1C-9D9B37AB8E03}"/>
+  <xr:revisionPtr revIDLastSave="3970" documentId="13_ncr:1_{A8E719AF-977A-4013-BC3F-0564FE4BBC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9C0C187-E26F-47C7-8BB9-4210AB72D3AF}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="144">
   <si>
     <t>Boneco</t>
   </si>
@@ -465,6 +465,12 @@
   </si>
   <si>
     <t>Para</t>
+  </si>
+  <si>
+    <t>Ronaldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João </t>
   </si>
 </sst>
 </file>
@@ -791,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O320"/>
+  <dimension ref="A1:O342"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -12020,6 +12026,776 @@
         <v>0</v>
       </c>
     </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>115</v>
+      </c>
+      <c r="C321">
+        <v>3</v>
+      </c>
+      <c r="D321">
+        <v>2</v>
+      </c>
+      <c r="E321">
+        <v>2</v>
+      </c>
+      <c r="F321">
+        <v>2</v>
+      </c>
+      <c r="G321">
+        <v>1</v>
+      </c>
+      <c r="H321">
+        <v>0</v>
+      </c>
+      <c r="I321">
+        <v>0</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>0</v>
+      </c>
+      <c r="L321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>36</v>
+      </c>
+      <c r="C322">
+        <v>3</v>
+      </c>
+      <c r="D322">
+        <v>2</v>
+      </c>
+      <c r="E322">
+        <v>2</v>
+      </c>
+      <c r="F322">
+        <v>3</v>
+      </c>
+      <c r="G322">
+        <v>1</v>
+      </c>
+      <c r="H322">
+        <v>0</v>
+      </c>
+      <c r="I322">
+        <v>0</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>0</v>
+      </c>
+      <c r="L322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>99</v>
+      </c>
+      <c r="C323">
+        <v>3</v>
+      </c>
+      <c r="D323">
+        <v>2</v>
+      </c>
+      <c r="E323">
+        <v>2</v>
+      </c>
+      <c r="F323">
+        <v>1</v>
+      </c>
+      <c r="G323">
+        <v>1</v>
+      </c>
+      <c r="H323">
+        <v>0</v>
+      </c>
+      <c r="I323">
+        <v>0</v>
+      </c>
+      <c r="J323">
+        <v>0</v>
+      </c>
+      <c r="K323">
+        <v>0</v>
+      </c>
+      <c r="L323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>142</v>
+      </c>
+      <c r="C324">
+        <v>3</v>
+      </c>
+      <c r="D324">
+        <v>2</v>
+      </c>
+      <c r="E324">
+        <v>2</v>
+      </c>
+      <c r="F324">
+        <v>1</v>
+      </c>
+      <c r="G324">
+        <v>1</v>
+      </c>
+      <c r="H324">
+        <v>0</v>
+      </c>
+      <c r="I324">
+        <v>0</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324">
+        <v>0</v>
+      </c>
+      <c r="L324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>32</v>
+      </c>
+      <c r="C325">
+        <v>3</v>
+      </c>
+      <c r="D325">
+        <v>2</v>
+      </c>
+      <c r="E325">
+        <v>2</v>
+      </c>
+      <c r="F325">
+        <v>1</v>
+      </c>
+      <c r="G325">
+        <v>1</v>
+      </c>
+      <c r="H325">
+        <v>0</v>
+      </c>
+      <c r="I325">
+        <v>0</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>29</v>
+      </c>
+      <c r="C326">
+        <v>3</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>4</v>
+      </c>
+      <c r="F326">
+        <v>1</v>
+      </c>
+      <c r="G326">
+        <v>1</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+      <c r="I326">
+        <v>0</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>0</v>
+      </c>
+      <c r="L326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>47</v>
+      </c>
+      <c r="C327">
+        <v>3</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>4</v>
+      </c>
+      <c r="F327">
+        <v>0</v>
+      </c>
+      <c r="G327">
+        <v>1</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+      <c r="I327">
+        <v>0</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>0</v>
+      </c>
+      <c r="L327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>30</v>
+      </c>
+      <c r="C328">
+        <v>3</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>4</v>
+      </c>
+      <c r="F328">
+        <v>2</v>
+      </c>
+      <c r="G328">
+        <v>1</v>
+      </c>
+      <c r="H328">
+        <v>0</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>0</v>
+      </c>
+      <c r="L328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>2</v>
+      </c>
+      <c r="C329">
+        <v>3</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>4</v>
+      </c>
+      <c r="F329">
+        <v>2</v>
+      </c>
+      <c r="G329">
+        <v>1</v>
+      </c>
+      <c r="H329">
+        <v>0</v>
+      </c>
+      <c r="I329">
+        <v>0</v>
+      </c>
+      <c r="J329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>0</v>
+      </c>
+      <c r="L329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>1</v>
+      </c>
+      <c r="C330">
+        <v>3</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>4</v>
+      </c>
+      <c r="F330">
+        <v>0</v>
+      </c>
+      <c r="G330">
+        <v>1</v>
+      </c>
+      <c r="H330">
+        <v>0</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>0</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>26</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>2</v>
+      </c>
+      <c r="E331">
+        <v>4</v>
+      </c>
+      <c r="F331">
+        <v>0</v>
+      </c>
+      <c r="G331">
+        <v>1</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+      <c r="I331">
+        <v>1</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>0</v>
+      </c>
+      <c r="L331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>41</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>2</v>
+      </c>
+      <c r="E332">
+        <v>4</v>
+      </c>
+      <c r="F332">
+        <v>0</v>
+      </c>
+      <c r="G332">
+        <v>1</v>
+      </c>
+      <c r="H332">
+        <v>0</v>
+      </c>
+      <c r="I332">
+        <v>1</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>0</v>
+      </c>
+      <c r="L332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>23</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>2</v>
+      </c>
+      <c r="E333">
+        <v>4</v>
+      </c>
+      <c r="F333">
+        <v>0</v>
+      </c>
+      <c r="G333">
+        <v>1</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
+      </c>
+      <c r="I333">
+        <v>1</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>0</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>59</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>2</v>
+      </c>
+      <c r="E334">
+        <v>4</v>
+      </c>
+      <c r="F334">
+        <v>1</v>
+      </c>
+      <c r="G334">
+        <v>1</v>
+      </c>
+      <c r="H334">
+        <v>0</v>
+      </c>
+      <c r="I334">
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334">
+        <v>0</v>
+      </c>
+      <c r="L334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>57</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>2</v>
+      </c>
+      <c r="E335">
+        <v>4</v>
+      </c>
+      <c r="F335">
+        <v>1</v>
+      </c>
+      <c r="G335">
+        <v>1</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
+      </c>
+      <c r="I335">
+        <v>1</v>
+      </c>
+      <c r="J335">
+        <v>0</v>
+      </c>
+      <c r="K335">
+        <v>0</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>20</v>
+      </c>
+      <c r="C336">
+        <v>5</v>
+      </c>
+      <c r="D336">
+        <v>2</v>
+      </c>
+      <c r="E336">
+        <v>1</v>
+      </c>
+      <c r="F336">
+        <v>2</v>
+      </c>
+      <c r="G336">
+        <v>1</v>
+      </c>
+      <c r="H336">
+        <v>1</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>5</v>
+      </c>
+      <c r="C337">
+        <v>5</v>
+      </c>
+      <c r="D337">
+        <v>2</v>
+      </c>
+      <c r="E337">
+        <v>1</v>
+      </c>
+      <c r="F337">
+        <v>2</v>
+      </c>
+      <c r="G337">
+        <v>1</v>
+      </c>
+      <c r="H337">
+        <v>1</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>0</v>
+      </c>
+      <c r="L337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>4</v>
+      </c>
+      <c r="C338">
+        <v>5</v>
+      </c>
+      <c r="D338">
+        <v>2</v>
+      </c>
+      <c r="E338">
+        <v>1</v>
+      </c>
+      <c r="F338">
+        <v>4</v>
+      </c>
+      <c r="G338">
+        <v>1</v>
+      </c>
+      <c r="H338">
+        <v>1</v>
+      </c>
+      <c r="I338">
+        <v>0</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <v>0</v>
+      </c>
+      <c r="L338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>6</v>
+      </c>
+      <c r="C339">
+        <v>5</v>
+      </c>
+      <c r="D339">
+        <v>2</v>
+      </c>
+      <c r="E339">
+        <v>1</v>
+      </c>
+      <c r="F339">
+        <v>3</v>
+      </c>
+      <c r="G339">
+        <v>1</v>
+      </c>
+      <c r="H339">
+        <v>1</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339">
+        <v>0</v>
+      </c>
+      <c r="L339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>3</v>
+      </c>
+      <c r="C340">
+        <v>5</v>
+      </c>
+      <c r="D340">
+        <v>2</v>
+      </c>
+      <c r="E340">
+        <v>1</v>
+      </c>
+      <c r="F340">
+        <v>1</v>
+      </c>
+      <c r="G340">
+        <v>1</v>
+      </c>
+      <c r="H340">
+        <v>1</v>
+      </c>
+      <c r="I340">
+        <v>0</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>0</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>143</v>
+      </c>
+      <c r="C341">
+        <v>6</v>
+      </c>
+      <c r="D341">
+        <v>3</v>
+      </c>
+      <c r="E341">
+        <v>6</v>
+      </c>
+      <c r="F341">
+        <v>0</v>
+      </c>
+      <c r="G341">
+        <v>1</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>13</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>124</v>
+      </c>
+      <c r="C342">
+        <v>6</v>
+      </c>
+      <c r="D342">
+        <v>3</v>
+      </c>
+      <c r="E342">
+        <v>6</v>
+      </c>
+      <c r="F342">
+        <v>0</v>
+      </c>
+      <c r="G342">
+        <v>1</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342">
+        <v>13</v>
+      </c>
+      <c r="L342">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L579" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
